--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982830</v>
+        <v>128982844</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>80174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601912</v>
+        <v>601669</v>
       </c>
       <c r="R11" t="n">
-        <v>6926296</v>
+        <v>6926519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,7 +1680,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128975867</v>
+        <v>128982830</v>
       </c>
       <c r="B12" t="n">
         <v>57723</v>
@@ -1714,21 +1709,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601927</v>
+        <v>601912</v>
       </c>
       <c r="R12" t="n">
-        <v>6926280</v>
+        <v>6926296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982794</v>
+        <v>128975867</v>
       </c>
       <c r="B13" t="n">
         <v>57723</v>
@@ -1821,16 +1811,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601565</v>
+        <v>601927</v>
       </c>
       <c r="R13" t="n">
-        <v>6926576</v>
+        <v>6926280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982844</v>
+        <v>128982794</v>
       </c>
       <c r="B14" t="n">
-        <v>80174</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1929,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601669</v>
+        <v>601565</v>
       </c>
       <c r="R14" t="n">
-        <v>6926519</v>
+        <v>6926576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,6 +1960,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982830</v>
+        <v>128982834</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601912</v>
+        <v>601569</v>
       </c>
       <c r="R12" t="n">
-        <v>6926296</v>
+        <v>6926585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128975867</v>
+        <v>128982830</v>
       </c>
       <c r="B13" t="n">
         <v>57723</v>
@@ -1811,21 +1811,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601927</v>
+        <v>601912</v>
       </c>
       <c r="R13" t="n">
-        <v>6926280</v>
+        <v>6926296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,7 +1884,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982794</v>
+        <v>128975867</v>
       </c>
       <c r="B14" t="n">
         <v>57723</v>
@@ -1918,16 +1913,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601565</v>
+        <v>601927</v>
       </c>
       <c r="R14" t="n">
-        <v>6926576</v>
+        <v>6926280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982834</v>
+        <v>128982794</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601569</v>
+        <v>601565</v>
       </c>
       <c r="R15" t="n">
-        <v>6926585</v>
+        <v>6926576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B16" t="n">
         <v>57723</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R16" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982826</v>
+        <v>128982816</v>
       </c>
       <c r="B17" t="n">
         <v>57723</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602022</v>
+        <v>601763</v>
       </c>
       <c r="R17" t="n">
-        <v>6926303</v>
+        <v>6926420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128982812</v>
+        <v>128982826</v>
       </c>
       <c r="B18" t="n">
         <v>57723</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601710</v>
+        <v>602022</v>
       </c>
       <c r="R18" t="n">
-        <v>6926335</v>
+        <v>6926303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982828</v>
+        <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601953</v>
+        <v>601810</v>
       </c>
       <c r="R21" t="n">
-        <v>6926305</v>
+        <v>6926372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128982840</v>
+        <v>128982828</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601810</v>
+        <v>601953</v>
       </c>
       <c r="R22" t="n">
-        <v>6926372</v>
+        <v>6926305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,6 +2776,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,7 +2810,7 @@
         <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3734,45 +3734,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128982838</v>
+        <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601914</v>
+        <v>601680</v>
       </c>
       <c r="R32" t="n">
-        <v>6926288</v>
+        <v>6926301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128975094</v>
+        <v>128982813</v>
       </c>
       <c r="B33" t="n">
         <v>57723</v>
@@ -3865,21 +3870,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601680</v>
+        <v>601751</v>
       </c>
       <c r="R33" t="n">
-        <v>6926301</v>
+        <v>6926340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982813</v>
+        <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601751</v>
+        <v>601914</v>
       </c>
       <c r="R34" t="n">
-        <v>6926340</v>
+        <v>6926288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982795</v>
+        <v>128982822</v>
       </c>
       <c r="B5" t="n">
         <v>57723</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601586</v>
+        <v>601990</v>
       </c>
       <c r="R5" t="n">
-        <v>6926499</v>
+        <v>6926320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982822</v>
+        <v>128982795</v>
       </c>
       <c r="B6" t="n">
         <v>57723</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601990</v>
+        <v>601586</v>
       </c>
       <c r="R6" t="n">
-        <v>6926320</v>
+        <v>6926499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
         <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R9" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982824</v>
+        <v>128982810</v>
       </c>
       <c r="B10" t="n">
         <v>57723</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602020</v>
+        <v>601716</v>
       </c>
       <c r="R10" t="n">
-        <v>6926329</v>
+        <v>6926368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982844</v>
+        <v>128982834</v>
       </c>
       <c r="B11" t="n">
-        <v>80174</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601669</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6926519</v>
+        <v>6926585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982834</v>
+        <v>128982844</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601569</v>
+        <v>601669</v>
       </c>
       <c r="R12" t="n">
-        <v>6926585</v>
+        <v>6926519</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982812</v>
+        <v>128982816</v>
       </c>
       <c r="B16" t="n">
         <v>57723</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601710</v>
+        <v>601763</v>
       </c>
       <c r="R16" t="n">
-        <v>6926335</v>
+        <v>6926420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B17" t="n">
         <v>57723</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R17" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128982826</v>
+        <v>128975179</v>
       </c>
       <c r="B18" t="n">
         <v>57723</v>
@@ -2326,16 +2326,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602022</v>
+        <v>601685</v>
       </c>
       <c r="R18" t="n">
-        <v>6926303</v>
+        <v>6926309</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,7 +2404,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982809</v>
+        <v>128982826</v>
       </c>
       <c r="B19" t="n">
         <v>57723</v>
@@ -2434,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601746</v>
+        <v>602022</v>
       </c>
       <c r="R19" t="n">
-        <v>6926365</v>
+        <v>6926303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128975179</v>
+        <v>128982809</v>
       </c>
       <c r="B20" t="n">
         <v>57723</v>
@@ -2530,21 +2535,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601685</v>
+        <v>601746</v>
       </c>
       <c r="R20" t="n">
-        <v>6926309</v>
+        <v>6926365</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,7 +2611,7 @@
         <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982806</v>
+        <v>128982796</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601714</v>
+        <v>601578</v>
       </c>
       <c r="R26" t="n">
-        <v>6926425</v>
+        <v>6926496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982796</v>
+        <v>128982827</v>
       </c>
       <c r="B27" t="n">
         <v>57723</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601578</v>
+        <v>602016</v>
       </c>
       <c r="R27" t="n">
-        <v>6926496</v>
+        <v>6926284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982818</v>
+        <v>128982806</v>
       </c>
       <c r="B28" t="n">
         <v>57723</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601845</v>
+        <v>601714</v>
       </c>
       <c r="R28" t="n">
-        <v>6926319</v>
+        <v>6926425</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982827</v>
+        <v>128982818</v>
       </c>
       <c r="B29" t="n">
         <v>57723</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602016</v>
+        <v>601845</v>
       </c>
       <c r="R29" t="n">
-        <v>6926284</v>
+        <v>6926319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3734,50 +3734,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128975094</v>
+        <v>128982838</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601680</v>
+        <v>601914</v>
       </c>
       <c r="R32" t="n">
-        <v>6926301</v>
+        <v>6926288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,7 +3836,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982813</v>
+        <v>128975094</v>
       </c>
       <c r="B33" t="n">
         <v>57723</v>
@@ -3870,16 +3865,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601751</v>
+        <v>601680</v>
       </c>
       <c r="R33" t="n">
-        <v>6926340</v>
+        <v>6926301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982838</v>
+        <v>128982813</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601914</v>
+        <v>601751</v>
       </c>
       <c r="R34" t="n">
-        <v>6926288</v>
+        <v>6926340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4147,7 +4147,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B36" t="n">
         <v>57723</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R36" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982800</v>
+        <v>128982801</v>
       </c>
       <c r="B37" t="n">
         <v>57723</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601632</v>
+        <v>601654</v>
       </c>
       <c r="R37" t="n">
-        <v>6926485</v>
+        <v>6926524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982808</v>
+        <v>128982807</v>
       </c>
       <c r="B41" t="n">
         <v>57723</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601744</v>
+        <v>601721</v>
       </c>
       <c r="R41" t="n">
-        <v>6926392</v>
+        <v>6926415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982807</v>
+        <v>128982831</v>
       </c>
       <c r="B42" t="n">
         <v>57723</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601721</v>
+        <v>601901</v>
       </c>
       <c r="R42" t="n">
-        <v>6926415</v>
+        <v>6926291</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982831</v>
+        <v>128982814</v>
       </c>
       <c r="B44" t="n">
         <v>57723</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601901</v>
+        <v>601765</v>
       </c>
       <c r="R44" t="n">
-        <v>6926291</v>
+        <v>6926339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982805</v>
+        <v>128982808</v>
       </c>
       <c r="B45" t="n">
         <v>57723</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601686</v>
+        <v>601744</v>
       </c>
       <c r="R45" t="n">
-        <v>6926478</v>
+        <v>6926392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982814</v>
+        <v>128982805</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601765</v>
+        <v>601686</v>
       </c>
       <c r="R47" t="n">
-        <v>6926339</v>
+        <v>6926478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5590,7 +5590,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982821</v>
+        <v>128982823</v>
       </c>
       <c r="B50" t="n">
         <v>57723</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>601965</v>
+        <v>602006</v>
       </c>
       <c r="R50" t="n">
-        <v>6926332</v>
+        <v>6926333</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B51" t="n">
         <v>57723</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R51" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B52" t="n">
         <v>57723</v>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R52" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982823</v>
+        <v>128982821</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602006</v>
+        <v>601965</v>
       </c>
       <c r="R53" t="n">
-        <v>6926333</v>
+        <v>6926332</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128975168</v>
+        <v>128982798</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -6037,21 +6037,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601683</v>
+        <v>601625</v>
       </c>
       <c r="R54" t="n">
-        <v>6926321</v>
+        <v>6926480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6088,7 +6083,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,7 +6110,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128982798</v>
+        <v>128975168</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -6144,16 +6139,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601625</v>
+        <v>601683</v>
       </c>
       <c r="R55" t="n">
-        <v>6926480</v>
+        <v>6926321</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6322,7 +6322,7 @@
         <v>128975492</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128982843</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982793</v>
+        <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601932</v>
+        <v>601716</v>
       </c>
       <c r="R8" t="n">
-        <v>6926305</v>
+        <v>6926368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1353,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982810</v>
+        <v>128982793</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601716</v>
+        <v>601932</v>
       </c>
       <c r="R10" t="n">
-        <v>6926368</v>
+        <v>6926305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1557,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982834</v>
+        <v>128982830</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601912</v>
       </c>
       <c r="R11" t="n">
-        <v>6926585</v>
+        <v>6926296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,45 +1685,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982844</v>
+        <v>128975867</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601669</v>
+        <v>601927</v>
       </c>
       <c r="R12" t="n">
-        <v>6926519</v>
+        <v>6926280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,6 +1761,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1792,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982830</v>
+        <v>128982794</v>
       </c>
       <c r="B13" t="n">
         <v>57723</v>
@@ -1817,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601912</v>
+        <v>601565</v>
       </c>
       <c r="R13" t="n">
-        <v>6926296</v>
+        <v>6926576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,50 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128975867</v>
+        <v>128982844</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601927</v>
+        <v>601669</v>
       </c>
       <c r="R14" t="n">
-        <v>6926280</v>
+        <v>6926519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,11 +1965,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982794</v>
+        <v>128982834</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601565</v>
+        <v>601569</v>
       </c>
       <c r="R15" t="n">
-        <v>6926576</v>
+        <v>6926585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B16" t="n">
         <v>57723</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R16" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982812</v>
+        <v>128982816</v>
       </c>
       <c r="B17" t="n">
         <v>57723</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601710</v>
+        <v>601763</v>
       </c>
       <c r="R17" t="n">
-        <v>6926335</v>
+        <v>6926420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128975179</v>
+        <v>128982826</v>
       </c>
       <c r="B18" t="n">
         <v>57723</v>
@@ -2326,21 +2326,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601685</v>
+        <v>602022</v>
       </c>
       <c r="R18" t="n">
-        <v>6926309</v>
+        <v>6926303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,7 +2399,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982826</v>
+        <v>128982809</v>
       </c>
       <c r="B19" t="n">
         <v>57723</v>
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602022</v>
+        <v>601746</v>
       </c>
       <c r="R19" t="n">
-        <v>6926303</v>
+        <v>6926365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,7 +2501,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128982809</v>
+        <v>128975179</v>
       </c>
       <c r="B20" t="n">
         <v>57723</v>
@@ -2535,16 +2530,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601746</v>
+        <v>601685</v>
       </c>
       <c r="R20" t="n">
-        <v>6926365</v>
+        <v>6926309</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982840</v>
+        <v>128982828</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601810</v>
+        <v>601953</v>
       </c>
       <c r="R21" t="n">
-        <v>6926372</v>
+        <v>6926305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128982828</v>
+        <v>128982840</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2740,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601953</v>
+        <v>601810</v>
       </c>
       <c r="R22" t="n">
-        <v>6926305</v>
+        <v>6926372</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,11 +2781,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982796</v>
+        <v>128982806</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601578</v>
+        <v>601714</v>
       </c>
       <c r="R26" t="n">
-        <v>6926496</v>
+        <v>6926425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982827</v>
+        <v>128982796</v>
       </c>
       <c r="B27" t="n">
         <v>57723</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602016</v>
+        <v>601578</v>
       </c>
       <c r="R27" t="n">
-        <v>6926284</v>
+        <v>6926496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982806</v>
+        <v>128982818</v>
       </c>
       <c r="B28" t="n">
         <v>57723</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601714</v>
+        <v>601845</v>
       </c>
       <c r="R28" t="n">
-        <v>6926425</v>
+        <v>6926319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982818</v>
+        <v>128982827</v>
       </c>
       <c r="B29" t="n">
         <v>57723</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601845</v>
+        <v>602016</v>
       </c>
       <c r="R29" t="n">
-        <v>6926319</v>
+        <v>6926284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982800</v>
+        <v>128982801</v>
       </c>
       <c r="B36" t="n">
         <v>57723</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601632</v>
+        <v>601654</v>
       </c>
       <c r="R36" t="n">
-        <v>6926485</v>
+        <v>6926524</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B37" t="n">
         <v>57723</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R37" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982807</v>
+        <v>128982808</v>
       </c>
       <c r="B41" t="n">
         <v>57723</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601721</v>
+        <v>601744</v>
       </c>
       <c r="R41" t="n">
-        <v>6926415</v>
+        <v>6926392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982831</v>
+        <v>128982807</v>
       </c>
       <c r="B42" t="n">
         <v>57723</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601901</v>
+        <v>601721</v>
       </c>
       <c r="R42" t="n">
-        <v>6926291</v>
+        <v>6926415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982814</v>
+        <v>128982831</v>
       </c>
       <c r="B44" t="n">
         <v>57723</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601765</v>
+        <v>601901</v>
       </c>
       <c r="R44" t="n">
-        <v>6926339</v>
+        <v>6926291</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982808</v>
+        <v>128982805</v>
       </c>
       <c r="B45" t="n">
         <v>57723</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601744</v>
+        <v>601686</v>
       </c>
       <c r="R45" t="n">
-        <v>6926392</v>
+        <v>6926478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982805</v>
+        <v>128982814</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601686</v>
+        <v>601765</v>
       </c>
       <c r="R47" t="n">
-        <v>6926478</v>
+        <v>6926339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5590,7 +5590,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982823</v>
+        <v>128982821</v>
       </c>
       <c r="B50" t="n">
         <v>57723</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602006</v>
+        <v>601965</v>
       </c>
       <c r="R50" t="n">
-        <v>6926333</v>
+        <v>6926332</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B51" t="n">
         <v>57723</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R51" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B52" t="n">
         <v>57723</v>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R52" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982821</v>
+        <v>128982823</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>601965</v>
+        <v>602006</v>
       </c>
       <c r="R53" t="n">
-        <v>6926332</v>
+        <v>6926333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128982798</v>
+        <v>128975168</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -6037,16 +6037,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601625</v>
+        <v>601683</v>
       </c>
       <c r="R54" t="n">
-        <v>6926480</v>
+        <v>6926321</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6083,7 +6088,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6110,7 +6115,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128975168</v>
+        <v>128982798</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -6139,21 +6144,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601683</v>
+        <v>601625</v>
       </c>
       <c r="R55" t="n">
-        <v>6926321</v>
+        <v>6926480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982822</v>
+        <v>128982795</v>
       </c>
       <c r="B5" t="n">
         <v>57723</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601990</v>
+        <v>601586</v>
       </c>
       <c r="R5" t="n">
-        <v>6926320</v>
+        <v>6926499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982795</v>
+        <v>128982822</v>
       </c>
       <c r="B6" t="n">
         <v>57723</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601586</v>
+        <v>601990</v>
       </c>
       <c r="R6" t="n">
-        <v>6926499</v>
+        <v>6926320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3734,45 +3734,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128982838</v>
+        <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601914</v>
+        <v>601680</v>
       </c>
       <c r="R32" t="n">
-        <v>6926288</v>
+        <v>6926301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128975094</v>
+        <v>128982813</v>
       </c>
       <c r="B33" t="n">
         <v>57723</v>
@@ -3865,21 +3870,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601680</v>
+        <v>601751</v>
       </c>
       <c r="R33" t="n">
-        <v>6926301</v>
+        <v>6926340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982813</v>
+        <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601751</v>
+        <v>601914</v>
       </c>
       <c r="R34" t="n">
-        <v>6926340</v>
+        <v>6926288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -2608,45 +2608,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982828</v>
+        <v>128975896</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601953</v>
+        <v>601925</v>
       </c>
       <c r="R21" t="n">
-        <v>6926305</v>
+        <v>6926296</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,11 +2683,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2807,49 +2806,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128975896</v>
+        <v>128982828</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601925</v>
+        <v>601953</v>
       </c>
       <c r="R23" t="n">
-        <v>6926296</v>
+        <v>6926305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,6 +2877,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128982817</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128982825</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128982795</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128982822</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128982811</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982810</v>
+        <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>91497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601716</v>
+        <v>601932</v>
       </c>
       <c r="R8" t="n">
-        <v>6926368</v>
+        <v>6926305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982824</v>
+        <v>128982810</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602020</v>
+        <v>601716</v>
       </c>
       <c r="R9" t="n">
-        <v>6926329</v>
+        <v>6926368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982793</v>
+        <v>128982824</v>
       </c>
       <c r="B10" t="n">
-        <v>91491</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601932</v>
+        <v>602020</v>
       </c>
       <c r="R10" t="n">
-        <v>6926305</v>
+        <v>6926329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982830</v>
+        <v>128982844</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>80179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601912</v>
+        <v>601669</v>
       </c>
       <c r="R11" t="n">
-        <v>6926296</v>
+        <v>6926519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128975867</v>
+        <v>128982834</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,16 +1691,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1714,21 +1709,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601927</v>
+        <v>601569</v>
       </c>
       <c r="R12" t="n">
-        <v>6926280</v>
+        <v>6926585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982794</v>
+        <v>128982830</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601565</v>
+        <v>601912</v>
       </c>
       <c r="R13" t="n">
-        <v>6926576</v>
+        <v>6926296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,45 +1884,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982844</v>
+        <v>128975867</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601669</v>
+        <v>601927</v>
       </c>
       <c r="R14" t="n">
-        <v>6926519</v>
+        <v>6926280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,6 +1960,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982834</v>
+        <v>128982794</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601569</v>
+        <v>601565</v>
       </c>
       <c r="R15" t="n">
-        <v>6926585</v>
+        <v>6926576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2096,7 +2096,7 @@
         <v>128982812</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128982816</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>128982826</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128982809</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>128975179</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>128975896</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>128982840</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128982828</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>128975731</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128982819</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128982806</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128982796</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128982818</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128982827</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>128982832</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>128975410</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3734,50 +3734,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128975094</v>
+        <v>128982838</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601680</v>
+        <v>601914</v>
       </c>
       <c r="R32" t="n">
-        <v>6926301</v>
+        <v>6926288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,10 +3836,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982813</v>
+        <v>128975094</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3870,16 +3865,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601751</v>
+        <v>601680</v>
       </c>
       <c r="R33" t="n">
-        <v>6926340</v>
+        <v>6926301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982838</v>
+        <v>128982813</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601914</v>
+        <v>601751</v>
       </c>
       <c r="R34" t="n">
-        <v>6926288</v>
+        <v>6926340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,7 +4048,7 @@
         <v>128982802</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>128982801</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128982800</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>128975670</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>128982820</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>128975430</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>128982808</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>128982807</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>128975206</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>128982831</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>128982805</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128982804</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>128982814</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>128982833</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128982797</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>128982821</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128975363</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128975260</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>128982823</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>128975168</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>128982798</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>128982815</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128975492</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128982843</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982844</v>
+        <v>128982834</v>
       </c>
       <c r="B11" t="n">
-        <v>80179</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601669</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6926519</v>
+        <v>6926585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982834</v>
+        <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,16 +1696,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601569</v>
+        <v>601912</v>
       </c>
       <c r="R12" t="n">
-        <v>6926585</v>
+        <v>6926296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982830</v>
+        <v>128975867</v>
       </c>
       <c r="B13" t="n">
         <v>57725</v>
@@ -1811,16 +1816,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601912</v>
+        <v>601927</v>
       </c>
       <c r="R13" t="n">
-        <v>6926296</v>
+        <v>6926280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128975867</v>
+        <v>128982794</v>
       </c>
       <c r="B14" t="n">
         <v>57725</v>
@@ -1913,21 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601927</v>
+        <v>601565</v>
       </c>
       <c r="R14" t="n">
-        <v>6926280</v>
+        <v>6926576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982794</v>
+        <v>128982844</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>80179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601565</v>
+        <v>601669</v>
       </c>
       <c r="R15" t="n">
-        <v>6926576</v>
+        <v>6926519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2067,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,49 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128975896</v>
+        <v>128982828</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601925</v>
+        <v>601953</v>
       </c>
       <c r="R21" t="n">
-        <v>6926296</v>
+        <v>6926305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,45 +2710,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128982840</v>
+        <v>128975896</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601810</v>
+        <v>601925</v>
       </c>
       <c r="R22" t="n">
-        <v>6926372</v>
+        <v>6926296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2806,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128982828</v>
+        <v>128982840</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2841,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601953</v>
+        <v>601810</v>
       </c>
       <c r="R23" t="n">
-        <v>6926305</v>
+        <v>6926372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,11 +2882,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982795</v>
+        <v>128982822</v>
       </c>
       <c r="B5" t="n">
         <v>57725</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601586</v>
+        <v>601990</v>
       </c>
       <c r="R5" t="n">
-        <v>6926499</v>
+        <v>6926320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982822</v>
+        <v>128982795</v>
       </c>
       <c r="B6" t="n">
         <v>57725</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601990</v>
+        <v>601586</v>
       </c>
       <c r="R6" t="n">
-        <v>6926320</v>
+        <v>6926499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982793</v>
+        <v>128982824</v>
       </c>
       <c r="B8" t="n">
-        <v>91497</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601932</v>
+        <v>602020</v>
       </c>
       <c r="R8" t="n">
-        <v>6926305</v>
+        <v>6926329</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1353,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982824</v>
+        <v>128982793</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602020</v>
+        <v>601932</v>
       </c>
       <c r="R10" t="n">
-        <v>6926329</v>
+        <v>6926305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1557,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982834</v>
+        <v>128982830</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601912</v>
       </c>
       <c r="R11" t="n">
-        <v>6926585</v>
+        <v>6926296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982830</v>
+        <v>128975867</v>
       </c>
       <c r="B12" t="n">
         <v>57725</v>
@@ -1714,16 +1714,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601912</v>
+        <v>601927</v>
       </c>
       <c r="R12" t="n">
-        <v>6926296</v>
+        <v>6926280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,7 +1792,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128975867</v>
+        <v>128982794</v>
       </c>
       <c r="B13" t="n">
         <v>57725</v>
@@ -1816,21 +1821,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601927</v>
+        <v>601565</v>
       </c>
       <c r="R13" t="n">
-        <v>6926280</v>
+        <v>6926576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982794</v>
+        <v>128982834</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601565</v>
+        <v>601569</v>
       </c>
       <c r="R14" t="n">
-        <v>6926576</v>
+        <v>6926585</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982812</v>
+        <v>128982816</v>
       </c>
       <c r="B16" t="n">
         <v>57725</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601710</v>
+        <v>601763</v>
       </c>
       <c r="R16" t="n">
-        <v>6926335</v>
+        <v>6926420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B17" t="n">
         <v>57725</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R17" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128982826</v>
+        <v>128975179</v>
       </c>
       <c r="B18" t="n">
         <v>57725</v>
@@ -2326,16 +2326,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602022</v>
+        <v>601685</v>
       </c>
       <c r="R18" t="n">
-        <v>6926303</v>
+        <v>6926309</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,7 +2404,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982809</v>
+        <v>128982826</v>
       </c>
       <c r="B19" t="n">
         <v>57725</v>
@@ -2434,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601746</v>
+        <v>602022</v>
       </c>
       <c r="R19" t="n">
-        <v>6926365</v>
+        <v>6926303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128975179</v>
+        <v>128982809</v>
       </c>
       <c r="B20" t="n">
         <v>57725</v>
@@ -2530,21 +2535,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601685</v>
+        <v>601746</v>
       </c>
       <c r="R20" t="n">
-        <v>6926309</v>
+        <v>6926365</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,45 +2608,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982828</v>
+        <v>128975896</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601953</v>
+        <v>601925</v>
       </c>
       <c r="R21" t="n">
-        <v>6926305</v>
+        <v>6926296</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,11 +2683,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,49 +2709,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128975896</v>
+        <v>128982828</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601925</v>
+        <v>601953</v>
       </c>
       <c r="R22" t="n">
-        <v>6926296</v>
+        <v>6926305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,6 +2780,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982806</v>
+        <v>128982796</v>
       </c>
       <c r="B26" t="n">
         <v>57725</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601714</v>
+        <v>601578</v>
       </c>
       <c r="R26" t="n">
-        <v>6926425</v>
+        <v>6926496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982796</v>
+        <v>128982827</v>
       </c>
       <c r="B27" t="n">
         <v>57725</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601578</v>
+        <v>602016</v>
       </c>
       <c r="R27" t="n">
-        <v>6926496</v>
+        <v>6926284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982818</v>
+        <v>128982806</v>
       </c>
       <c r="B28" t="n">
         <v>57725</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601845</v>
+        <v>601714</v>
       </c>
       <c r="R28" t="n">
-        <v>6926319</v>
+        <v>6926425</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982827</v>
+        <v>128982818</v>
       </c>
       <c r="B29" t="n">
         <v>57725</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602016</v>
+        <v>601845</v>
       </c>
       <c r="R29" t="n">
-        <v>6926284</v>
+        <v>6926319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3734,45 +3734,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128982838</v>
+        <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601914</v>
+        <v>601680</v>
       </c>
       <c r="R32" t="n">
-        <v>6926288</v>
+        <v>6926301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128975094</v>
+        <v>128982813</v>
       </c>
       <c r="B33" t="n">
         <v>57725</v>
@@ -3865,21 +3870,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601680</v>
+        <v>601751</v>
       </c>
       <c r="R33" t="n">
-        <v>6926301</v>
+        <v>6926340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982813</v>
+        <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601751</v>
+        <v>601914</v>
       </c>
       <c r="R34" t="n">
-        <v>6926340</v>
+        <v>6926288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4147,7 +4147,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B36" t="n">
         <v>57725</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R36" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982800</v>
+        <v>128982801</v>
       </c>
       <c r="B37" t="n">
         <v>57725</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601632</v>
+        <v>601654</v>
       </c>
       <c r="R37" t="n">
-        <v>6926485</v>
+        <v>6926524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982808</v>
+        <v>128982807</v>
       </c>
       <c r="B41" t="n">
         <v>57725</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601744</v>
+        <v>601721</v>
       </c>
       <c r="R41" t="n">
-        <v>6926392</v>
+        <v>6926415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982807</v>
+        <v>128982831</v>
       </c>
       <c r="B42" t="n">
         <v>57725</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601721</v>
+        <v>601901</v>
       </c>
       <c r="R42" t="n">
-        <v>6926415</v>
+        <v>6926291</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982831</v>
+        <v>128982814</v>
       </c>
       <c r="B44" t="n">
         <v>57725</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601901</v>
+        <v>601765</v>
       </c>
       <c r="R44" t="n">
-        <v>6926291</v>
+        <v>6926339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982805</v>
+        <v>128982808</v>
       </c>
       <c r="B45" t="n">
         <v>57725</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601686</v>
+        <v>601744</v>
       </c>
       <c r="R45" t="n">
-        <v>6926478</v>
+        <v>6926392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982814</v>
+        <v>128982805</v>
       </c>
       <c r="B47" t="n">
         <v>57725</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601765</v>
+        <v>601686</v>
       </c>
       <c r="R47" t="n">
-        <v>6926339</v>
+        <v>6926478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5590,7 +5590,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982821</v>
+        <v>128982823</v>
       </c>
       <c r="B50" t="n">
         <v>57725</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>601965</v>
+        <v>602006</v>
       </c>
       <c r="R50" t="n">
-        <v>6926332</v>
+        <v>6926333</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B51" t="n">
         <v>57725</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R51" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B52" t="n">
         <v>57725</v>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R52" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982823</v>
+        <v>128982821</v>
       </c>
       <c r="B53" t="n">
         <v>57725</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602006</v>
+        <v>601965</v>
       </c>
       <c r="R53" t="n">
-        <v>6926333</v>
+        <v>6926332</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128975168</v>
+        <v>128982798</v>
       </c>
       <c r="B54" t="n">
         <v>57725</v>
@@ -6037,21 +6037,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601683</v>
+        <v>601625</v>
       </c>
       <c r="R54" t="n">
-        <v>6926321</v>
+        <v>6926480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6088,7 +6083,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,7 +6110,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128982798</v>
+        <v>128975168</v>
       </c>
       <c r="B55" t="n">
         <v>57725</v>
@@ -6144,16 +6139,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601625</v>
+        <v>601683</v>
       </c>
       <c r="R55" t="n">
-        <v>6926480</v>
+        <v>6926321</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128982817</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128982825</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982822</v>
+        <v>128982795</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601990</v>
+        <v>601586</v>
       </c>
       <c r="R5" t="n">
-        <v>6926320</v>
+        <v>6926499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982795</v>
+        <v>128982822</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601586</v>
+        <v>601990</v>
       </c>
       <c r="R6" t="n">
-        <v>6926499</v>
+        <v>6926320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>128982811</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982824</v>
+        <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602020</v>
+        <v>601716</v>
       </c>
       <c r="R8" t="n">
-        <v>6926329</v>
+        <v>6926368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R9" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,7 +1489,7 @@
         <v>128982793</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982830</v>
+        <v>128982834</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601912</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6926296</v>
+        <v>6926585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128975867</v>
+        <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,21 +1714,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601927</v>
+        <v>601912</v>
       </c>
       <c r="R12" t="n">
-        <v>6926280</v>
+        <v>6926296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982794</v>
+        <v>128975867</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,16 +1816,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601565</v>
+        <v>601927</v>
       </c>
       <c r="R13" t="n">
-        <v>6926576</v>
+        <v>6926280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982834</v>
+        <v>128982794</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601569</v>
+        <v>601565</v>
       </c>
       <c r="R14" t="n">
-        <v>6926585</v>
+        <v>6926576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,7 +1999,7 @@
         <v>128982844</v>
       </c>
       <c r="B15" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,10 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R16" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982812</v>
+        <v>128982816</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601710</v>
+        <v>601763</v>
       </c>
       <c r="R17" t="n">
-        <v>6926335</v>
+        <v>6926420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128975179</v>
+        <v>128982826</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2326,21 +2326,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601685</v>
+        <v>602022</v>
       </c>
       <c r="R18" t="n">
-        <v>6926309</v>
+        <v>6926303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982826</v>
+        <v>128982809</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602022</v>
+        <v>601746</v>
       </c>
       <c r="R19" t="n">
-        <v>6926303</v>
+        <v>6926365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,10 +2501,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128982809</v>
+        <v>128975179</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,16 +2530,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601746</v>
+        <v>601685</v>
       </c>
       <c r="R20" t="n">
-        <v>6926365</v>
+        <v>6926309</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,49 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128975896</v>
+        <v>128982828</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601925</v>
+        <v>601953</v>
       </c>
       <c r="R21" t="n">
-        <v>6926296</v>
+        <v>6926305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,45 +2710,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128982828</v>
+        <v>128975896</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601953</v>
+        <v>601925</v>
       </c>
       <c r="R22" t="n">
-        <v>6926305</v>
+        <v>6926296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,11 +2785,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2814,7 +2814,7 @@
         <v>128982840</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>128975731</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128982819</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982796</v>
+        <v>128982806</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601578</v>
+        <v>601714</v>
       </c>
       <c r="R26" t="n">
-        <v>6926496</v>
+        <v>6926425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982827</v>
+        <v>128982796</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602016</v>
+        <v>601578</v>
       </c>
       <c r="R27" t="n">
-        <v>6926284</v>
+        <v>6926496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982806</v>
+        <v>128982818</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601714</v>
+        <v>601845</v>
       </c>
       <c r="R28" t="n">
-        <v>6926425</v>
+        <v>6926319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982818</v>
+        <v>128982827</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601845</v>
+        <v>602016</v>
       </c>
       <c r="R29" t="n">
-        <v>6926319</v>
+        <v>6926284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,7 +3528,7 @@
         <v>128982832</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>128975410</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3734,50 +3734,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128975094</v>
+        <v>128982838</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601680</v>
+        <v>601914</v>
       </c>
       <c r="R32" t="n">
-        <v>6926301</v>
+        <v>6926288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,10 +3836,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982813</v>
+        <v>128975094</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3870,16 +3865,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601751</v>
+        <v>601680</v>
       </c>
       <c r="R33" t="n">
-        <v>6926340</v>
+        <v>6926301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982838</v>
+        <v>128982813</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601914</v>
+        <v>601751</v>
       </c>
       <c r="R34" t="n">
-        <v>6926288</v>
+        <v>6926340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4048,7 +4048,7 @@
         <v>128982802</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4147,10 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982800</v>
+        <v>128982801</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601632</v>
+        <v>601654</v>
       </c>
       <c r="R36" t="n">
-        <v>6926485</v>
+        <v>6926524</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,10 +4249,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R37" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,7 +4354,7 @@
         <v>128975670</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>128982820</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>128975430</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982807</v>
+        <v>128982808</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601721</v>
+        <v>601744</v>
       </c>
       <c r="R41" t="n">
-        <v>6926415</v>
+        <v>6926392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982831</v>
+        <v>128982807</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601901</v>
+        <v>601721</v>
       </c>
       <c r="R42" t="n">
-        <v>6926291</v>
+        <v>6926415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4874,7 +4874,7 @@
         <v>128975206</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982814</v>
+        <v>128982831</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601765</v>
+        <v>601901</v>
       </c>
       <c r="R44" t="n">
-        <v>6926339</v>
+        <v>6926291</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,10 +5080,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982808</v>
+        <v>128982805</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601744</v>
+        <v>601686</v>
       </c>
       <c r="R45" t="n">
-        <v>6926392</v>
+        <v>6926478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5185,7 +5185,7 @@
         <v>128982804</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982805</v>
+        <v>128982814</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601686</v>
+        <v>601765</v>
       </c>
       <c r="R47" t="n">
-        <v>6926478</v>
+        <v>6926339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5389,7 +5389,7 @@
         <v>128982833</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128982797</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982823</v>
+        <v>128982821</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602006</v>
+        <v>601965</v>
       </c>
       <c r="R50" t="n">
-        <v>6926333</v>
+        <v>6926332</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,10 +5692,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R51" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R52" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982821</v>
+        <v>128982823</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>601965</v>
+        <v>602006</v>
       </c>
       <c r="R53" t="n">
-        <v>6926332</v>
+        <v>6926333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,10 +6008,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128982798</v>
+        <v>128975168</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6037,16 +6037,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601625</v>
+        <v>601683</v>
       </c>
       <c r="R54" t="n">
-        <v>6926480</v>
+        <v>6926321</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6083,7 +6088,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6110,10 +6115,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128975168</v>
+        <v>128982798</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6139,21 +6144,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601683</v>
+        <v>601625</v>
       </c>
       <c r="R55" t="n">
-        <v>6926321</v>
+        <v>6926480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6220,7 +6220,7 @@
         <v>128982815</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128975492</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128982843</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982810</v>
+        <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601716</v>
+        <v>601932</v>
       </c>
       <c r="R8" t="n">
-        <v>6926368</v>
+        <v>6926305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982793</v>
+        <v>128982810</v>
       </c>
       <c r="B10" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601932</v>
+        <v>601716</v>
       </c>
       <c r="R10" t="n">
-        <v>6926305</v>
+        <v>6926368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982834</v>
+        <v>128982844</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>80181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601669</v>
       </c>
       <c r="R11" t="n">
-        <v>6926585</v>
+        <v>6926519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982830</v>
+        <v>128982834</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,16 +1691,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1720,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601912</v>
+        <v>601569</v>
       </c>
       <c r="R12" t="n">
-        <v>6926296</v>
+        <v>6926585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128975867</v>
+        <v>128982794</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1816,21 +1811,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601927</v>
+        <v>601565</v>
       </c>
       <c r="R13" t="n">
-        <v>6926280</v>
+        <v>6926576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,7 +1884,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982794</v>
+        <v>128982830</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1929,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601565</v>
+        <v>601912</v>
       </c>
       <c r="R14" t="n">
-        <v>6926576</v>
+        <v>6926296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1959,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,45 +1986,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982844</v>
+        <v>128975867</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601669</v>
+        <v>601927</v>
       </c>
       <c r="R15" t="n">
-        <v>6926519</v>
+        <v>6926280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982828</v>
+        <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601953</v>
+        <v>601810</v>
       </c>
       <c r="R21" t="n">
-        <v>6926305</v>
+        <v>6926372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,49 +2705,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128975896</v>
+        <v>128982828</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601925</v>
+        <v>601953</v>
       </c>
       <c r="R22" t="n">
-        <v>6926296</v>
+        <v>6926305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,6 +2776,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,45 +2807,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128982840</v>
+        <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601810</v>
+        <v>601925</v>
       </c>
       <c r="R23" t="n">
-        <v>6926372</v>
+        <v>6926296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128975731</v>
+        <v>128982819</v>
       </c>
       <c r="B24" t="n">
         <v>57727</v>
@@ -2937,21 +2937,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601908</v>
+        <v>601851</v>
       </c>
       <c r="R24" t="n">
-        <v>6926265</v>
+        <v>6926322</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2988,7 +2983,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3015,7 +3010,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128982819</v>
+        <v>128975731</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3044,16 +3039,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601851</v>
+        <v>601908</v>
       </c>
       <c r="R25" t="n">
-        <v>6926322</v>
+        <v>6926265</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982796</v>
+        <v>128982827</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601578</v>
+        <v>602016</v>
       </c>
       <c r="R27" t="n">
-        <v>6926496</v>
+        <v>6926284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982818</v>
+        <v>128982796</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601845</v>
+        <v>601578</v>
       </c>
       <c r="R28" t="n">
-        <v>6926319</v>
+        <v>6926496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982827</v>
+        <v>128982818</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602016</v>
+        <v>601845</v>
       </c>
       <c r="R29" t="n">
-        <v>6926284</v>
+        <v>6926319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3734,45 +3734,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128982838</v>
+        <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601914</v>
+        <v>601680</v>
       </c>
       <c r="R32" t="n">
-        <v>6926288</v>
+        <v>6926301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,50 +3841,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128975094</v>
+        <v>128982838</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601680</v>
+        <v>601914</v>
       </c>
       <c r="R33" t="n">
-        <v>6926301</v>
+        <v>6926288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128975670</v>
+        <v>128982820</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4380,21 +4380,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601875</v>
+        <v>601839</v>
       </c>
       <c r="R38" t="n">
-        <v>6926213</v>
+        <v>6926335</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4431,7 +4426,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4458,7 +4453,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128982820</v>
+        <v>128975670</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4487,16 +4482,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601839</v>
+        <v>601875</v>
       </c>
       <c r="R39" t="n">
-        <v>6926335</v>
+        <v>6926213</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982808</v>
+        <v>128982831</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601744</v>
+        <v>601901</v>
       </c>
       <c r="R41" t="n">
-        <v>6926392</v>
+        <v>6926291</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982807</v>
+        <v>128982805</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601721</v>
+        <v>601686</v>
       </c>
       <c r="R42" t="n">
-        <v>6926415</v>
+        <v>6926478</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4871,7 +4871,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128975206</v>
+        <v>128982804</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4900,21 +4900,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601689</v>
+        <v>601703</v>
       </c>
       <c r="R43" t="n">
-        <v>6926299</v>
+        <v>6926487</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,7 +4946,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4978,7 +4973,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982831</v>
+        <v>128982833</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5013,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601901</v>
+        <v>601691</v>
       </c>
       <c r="R44" t="n">
-        <v>6926291</v>
+        <v>6926349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5048,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5075,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982805</v>
+        <v>128975206</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5109,16 +5104,21 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601686</v>
+        <v>601689</v>
       </c>
       <c r="R45" t="n">
-        <v>6926478</v>
+        <v>6926299</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5182,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982804</v>
+        <v>128982814</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601703</v>
+        <v>601765</v>
       </c>
       <c r="R46" t="n">
-        <v>6926487</v>
+        <v>6926339</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982814</v>
+        <v>128982808</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601765</v>
+        <v>601744</v>
       </c>
       <c r="R47" t="n">
-        <v>6926339</v>
+        <v>6926392</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128982833</v>
+        <v>128982807</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601691</v>
+        <v>601721</v>
       </c>
       <c r="R48" t="n">
-        <v>6926349</v>
+        <v>6926415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975363</v>
+        <v>128982823</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5721,21 +5721,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601787</v>
+        <v>602006</v>
       </c>
       <c r="R51" t="n">
-        <v>6926265</v>
+        <v>6926333</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5767,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,7 +5794,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5839,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R52" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,7 +5901,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982823</v>
+        <v>128975260</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5935,16 +5930,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602006</v>
+        <v>601702</v>
       </c>
       <c r="R53" t="n">
-        <v>6926333</v>
+        <v>6926319</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982806</v>
+        <v>128982796</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601714</v>
+        <v>601578</v>
       </c>
       <c r="R26" t="n">
-        <v>6926425</v>
+        <v>6926496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982827</v>
+        <v>128982818</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602016</v>
+        <v>601845</v>
       </c>
       <c r="R27" t="n">
-        <v>6926284</v>
+        <v>6926319</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982796</v>
+        <v>128982806</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601578</v>
+        <v>601714</v>
       </c>
       <c r="R28" t="n">
-        <v>6926496</v>
+        <v>6926425</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982818</v>
+        <v>128982827</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601845</v>
+        <v>602016</v>
       </c>
       <c r="R29" t="n">
-        <v>6926319</v>
+        <v>6926284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982831</v>
+        <v>128975206</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4696,16 +4696,21 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601901</v>
+        <v>601689</v>
       </c>
       <c r="R41" t="n">
-        <v>6926291</v>
+        <v>6926299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4742,7 +4747,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4769,7 +4774,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982805</v>
+        <v>128982814</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4804,10 +4809,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601686</v>
+        <v>601765</v>
       </c>
       <c r="R42" t="n">
-        <v>6926478</v>
+        <v>6926339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4849,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4871,7 +4876,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128982804</v>
+        <v>128982808</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4906,10 +4911,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601703</v>
+        <v>601744</v>
       </c>
       <c r="R43" t="n">
-        <v>6926487</v>
+        <v>6926392</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982833</v>
+        <v>128982807</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5008,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601691</v>
+        <v>601721</v>
       </c>
       <c r="R44" t="n">
-        <v>6926349</v>
+        <v>6926415</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128975206</v>
+        <v>128982831</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5104,21 +5109,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601689</v>
+        <v>601901</v>
       </c>
       <c r="R45" t="n">
-        <v>6926299</v>
+        <v>6926291</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5182,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982814</v>
+        <v>128982805</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601765</v>
+        <v>601686</v>
       </c>
       <c r="R46" t="n">
-        <v>6926339</v>
+        <v>6926478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982808</v>
+        <v>128982804</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601744</v>
+        <v>601703</v>
       </c>
       <c r="R47" t="n">
-        <v>6926392</v>
+        <v>6926487</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128982807</v>
+        <v>128982833</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601721</v>
+        <v>601691</v>
       </c>
       <c r="R48" t="n">
-        <v>6926415</v>
+        <v>6926349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982824</v>
+        <v>128982810</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602020</v>
+        <v>601716</v>
       </c>
       <c r="R9" t="n">
-        <v>6926329</v>
+        <v>6926368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R10" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982844</v>
+        <v>128982834</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601669</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6926519</v>
+        <v>6926585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982834</v>
+        <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,16 +1696,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601569</v>
+        <v>601912</v>
       </c>
       <c r="R12" t="n">
-        <v>6926585</v>
+        <v>6926296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982794</v>
+        <v>128975867</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1811,16 +1816,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601565</v>
+        <v>601927</v>
       </c>
       <c r="R13" t="n">
-        <v>6926576</v>
+        <v>6926280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982830</v>
+        <v>128982794</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1919,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601912</v>
+        <v>601565</v>
       </c>
       <c r="R14" t="n">
-        <v>6926296</v>
+        <v>6926576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,50 +1996,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128975867</v>
+        <v>128982844</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601927</v>
+        <v>601669</v>
       </c>
       <c r="R15" t="n">
-        <v>6926280</v>
+        <v>6926519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2067,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2810,7 +2810,7 @@
         <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128982819</v>
+        <v>128975731</v>
       </c>
       <c r="B24" t="n">
         <v>57727</v>
@@ -2937,16 +2937,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601851</v>
+        <v>601908</v>
       </c>
       <c r="R24" t="n">
-        <v>6926322</v>
+        <v>6926265</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,7 +2988,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3010,7 +3015,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128975731</v>
+        <v>128982819</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3039,21 +3044,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601908</v>
+        <v>601851</v>
       </c>
       <c r="R25" t="n">
-        <v>6926265</v>
+        <v>6926322</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982796</v>
+        <v>128982806</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601578</v>
+        <v>601714</v>
       </c>
       <c r="R26" t="n">
-        <v>6926496</v>
+        <v>6926425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982818</v>
+        <v>128982796</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601845</v>
+        <v>601578</v>
       </c>
       <c r="R27" t="n">
-        <v>6926319</v>
+        <v>6926496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982806</v>
+        <v>128982818</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601714</v>
+        <v>601845</v>
       </c>
       <c r="R28" t="n">
-        <v>6926425</v>
+        <v>6926319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3841,32 +3841,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982838</v>
+        <v>128982813</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601914</v>
+        <v>601751</v>
       </c>
       <c r="R33" t="n">
-        <v>6926288</v>
+        <v>6926340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982813</v>
+        <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601751</v>
+        <v>601914</v>
       </c>
       <c r="R34" t="n">
-        <v>6926340</v>
+        <v>6926288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128982820</v>
+        <v>128975670</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4380,16 +4380,21 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601839</v>
+        <v>601875</v>
       </c>
       <c r="R38" t="n">
-        <v>6926335</v>
+        <v>6926213</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,7 +4431,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,7 +4458,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128975670</v>
+        <v>128982820</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4482,21 +4487,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601875</v>
+        <v>601839</v>
       </c>
       <c r="R39" t="n">
-        <v>6926213</v>
+        <v>6926335</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128975206</v>
+        <v>128982808</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4696,21 +4696,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601689</v>
+        <v>601744</v>
       </c>
       <c r="R41" t="n">
-        <v>6926299</v>
+        <v>6926392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,7 +4742,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982814</v>
+        <v>128982807</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4809,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601765</v>
+        <v>601721</v>
       </c>
       <c r="R42" t="n">
-        <v>6926339</v>
+        <v>6926415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4876,7 +4871,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128982808</v>
+        <v>128975206</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4905,16 +4900,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601744</v>
+        <v>601689</v>
       </c>
       <c r="R43" t="n">
-        <v>6926392</v>
+        <v>6926299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982807</v>
+        <v>128982831</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601721</v>
+        <v>601901</v>
       </c>
       <c r="R44" t="n">
-        <v>6926415</v>
+        <v>6926291</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982831</v>
+        <v>128982805</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601901</v>
+        <v>601686</v>
       </c>
       <c r="R45" t="n">
-        <v>6926291</v>
+        <v>6926478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982805</v>
+        <v>128982804</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601686</v>
+        <v>601703</v>
       </c>
       <c r="R46" t="n">
-        <v>6926478</v>
+        <v>6926487</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982804</v>
+        <v>128982814</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601703</v>
+        <v>601765</v>
       </c>
       <c r="R47" t="n">
-        <v>6926487</v>
+        <v>6926339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128982823</v>
+        <v>128975363</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5721,16 +5721,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>602006</v>
+        <v>601787</v>
       </c>
       <c r="R51" t="n">
-        <v>6926333</v>
+        <v>6926265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5767,7 +5772,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5794,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5834,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R52" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128975260</v>
+        <v>128982823</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5930,21 +5935,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>601702</v>
+        <v>602006</v>
       </c>
       <c r="R53" t="n">
-        <v>6926319</v>
+        <v>6926333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128982817</v>
+        <v>128982825</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601807</v>
+        <v>602015</v>
       </c>
       <c r="R3" t="n">
-        <v>6926447</v>
+        <v>6926321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128982825</v>
+        <v>128982817</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602015</v>
+        <v>601807</v>
       </c>
       <c r="R4" t="n">
-        <v>6926321</v>
+        <v>6926447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982793</v>
+        <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601932</v>
+        <v>601716</v>
       </c>
       <c r="R8" t="n">
-        <v>6926305</v>
+        <v>6926368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1353,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R9" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982824</v>
+        <v>128982793</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602020</v>
+        <v>601932</v>
       </c>
       <c r="R10" t="n">
-        <v>6926329</v>
+        <v>6926305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1557,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982830</v>
+        <v>128975867</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1714,16 +1714,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601912</v>
+        <v>601927</v>
       </c>
       <c r="R12" t="n">
-        <v>6926296</v>
+        <v>6926280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,7 +1792,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128975867</v>
+        <v>128982794</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1816,21 +1821,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601927</v>
+        <v>601565</v>
       </c>
       <c r="R13" t="n">
-        <v>6926280</v>
+        <v>6926576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982794</v>
+        <v>128982830</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601565</v>
+        <v>601912</v>
       </c>
       <c r="R14" t="n">
-        <v>6926576</v>
+        <v>6926296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982840</v>
+        <v>128982828</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601810</v>
+        <v>601953</v>
       </c>
       <c r="R21" t="n">
-        <v>6926372</v>
+        <v>6926305</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2679,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,45 +2710,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128982828</v>
+        <v>128975896</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601953</v>
+        <v>601925</v>
       </c>
       <c r="R22" t="n">
-        <v>6926305</v>
+        <v>6926296</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,11 +2785,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2807,49 +2811,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128975896</v>
+        <v>128982840</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601925</v>
+        <v>601810</v>
       </c>
       <c r="R23" t="n">
-        <v>6926296</v>
+        <v>6926372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3734,50 +3734,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128975094</v>
+        <v>128982838</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601680</v>
+        <v>601914</v>
       </c>
       <c r="R32" t="n">
-        <v>6926301</v>
+        <v>6926288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,7 +3836,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982813</v>
+        <v>128975094</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3870,16 +3865,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601751</v>
+        <v>601680</v>
       </c>
       <c r="R33" t="n">
-        <v>6926340</v>
+        <v>6926301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982838</v>
+        <v>128982813</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601914</v>
+        <v>601751</v>
       </c>
       <c r="R34" t="n">
-        <v>6926288</v>
+        <v>6926340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128982825</v>
+        <v>128982817</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602015</v>
+        <v>601807</v>
       </c>
       <c r="R3" t="n">
-        <v>6926321</v>
+        <v>6926447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128982817</v>
+        <v>128982825</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601807</v>
+        <v>602015</v>
       </c>
       <c r="R4" t="n">
-        <v>6926447</v>
+        <v>6926321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982810</v>
+        <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601716</v>
+        <v>601932</v>
       </c>
       <c r="R8" t="n">
-        <v>6926368</v>
+        <v>6926305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982824</v>
+        <v>128982810</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1419,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602020</v>
+        <v>601716</v>
       </c>
       <c r="R9" t="n">
-        <v>6926329</v>
+        <v>6926368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982793</v>
+        <v>128982824</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601932</v>
+        <v>602020</v>
       </c>
       <c r="R10" t="n">
-        <v>6926305</v>
+        <v>6926329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982834</v>
+        <v>128982844</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>80181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601669</v>
       </c>
       <c r="R11" t="n">
-        <v>6926585</v>
+        <v>6926519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128975867</v>
+        <v>128982834</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,16 +1691,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1714,21 +1709,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601927</v>
+        <v>601569</v>
       </c>
       <c r="R12" t="n">
-        <v>6926280</v>
+        <v>6926585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1792,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982794</v>
+        <v>128982830</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1827,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601565</v>
+        <v>601912</v>
       </c>
       <c r="R13" t="n">
-        <v>6926576</v>
+        <v>6926296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,7 +1884,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982830</v>
+        <v>128975867</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1923,16 +1913,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601912</v>
+        <v>601927</v>
       </c>
       <c r="R14" t="n">
-        <v>6926296</v>
+        <v>6926280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,32 +1991,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982844</v>
+        <v>128982794</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601669</v>
+        <v>601565</v>
       </c>
       <c r="R15" t="n">
-        <v>6926519</v>
+        <v>6926576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982828</v>
+        <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601953</v>
+        <v>601810</v>
       </c>
       <c r="R21" t="n">
-        <v>6926305</v>
+        <v>6926372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,49 +2705,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128975896</v>
+        <v>128982828</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601925</v>
+        <v>601953</v>
       </c>
       <c r="R22" t="n">
-        <v>6926296</v>
+        <v>6926305</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,6 +2776,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2811,45 +2807,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128982840</v>
+        <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601810</v>
+        <v>601925</v>
       </c>
       <c r="R23" t="n">
-        <v>6926372</v>
+        <v>6926296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3734,45 +3734,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128982838</v>
+        <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601914</v>
+        <v>601680</v>
       </c>
       <c r="R32" t="n">
-        <v>6926288</v>
+        <v>6926301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128975094</v>
+        <v>128982813</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3865,21 +3870,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601680</v>
+        <v>601751</v>
       </c>
       <c r="R33" t="n">
-        <v>6926301</v>
+        <v>6926340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982813</v>
+        <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601751</v>
+        <v>601914</v>
       </c>
       <c r="R34" t="n">
-        <v>6926340</v>
+        <v>6926288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982808</v>
+        <v>128982814</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601744</v>
+        <v>601765</v>
       </c>
       <c r="R41" t="n">
-        <v>6926392</v>
+        <v>6926339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982807</v>
+        <v>128982808</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601721</v>
+        <v>601744</v>
       </c>
       <c r="R42" t="n">
-        <v>6926415</v>
+        <v>6926392</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128975206</v>
+        <v>128982807</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4900,21 +4900,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601689</v>
+        <v>601721</v>
       </c>
       <c r="R43" t="n">
-        <v>6926299</v>
+        <v>6926415</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,7 +4946,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4978,7 +4973,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982831</v>
+        <v>128975206</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5007,16 +5002,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601901</v>
+        <v>601689</v>
       </c>
       <c r="R44" t="n">
-        <v>6926291</v>
+        <v>6926299</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982805</v>
+        <v>128982831</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601686</v>
+        <v>601901</v>
       </c>
       <c r="R45" t="n">
-        <v>6926478</v>
+        <v>6926291</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982804</v>
+        <v>128982805</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601703</v>
+        <v>601686</v>
       </c>
       <c r="R46" t="n">
-        <v>6926487</v>
+        <v>6926478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982814</v>
+        <v>128982804</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601765</v>
+        <v>601703</v>
       </c>
       <c r="R47" t="n">
-        <v>6926339</v>
+        <v>6926487</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982793</v>
+        <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601932</v>
+        <v>601716</v>
       </c>
       <c r="R8" t="n">
-        <v>6926305</v>
+        <v>6926368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1353,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R9" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982824</v>
+        <v>128982793</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602020</v>
+        <v>601932</v>
       </c>
       <c r="R10" t="n">
-        <v>6926329</v>
+        <v>6926305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1557,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982844</v>
+        <v>128982834</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601669</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6926519</v>
+        <v>6926585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982834</v>
+        <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,16 +1696,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601569</v>
+        <v>601912</v>
       </c>
       <c r="R12" t="n">
-        <v>6926585</v>
+        <v>6926296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982830</v>
+        <v>128975867</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1811,16 +1816,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601912</v>
+        <v>601927</v>
       </c>
       <c r="R13" t="n">
-        <v>6926296</v>
+        <v>6926280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128975867</v>
+        <v>128982794</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1913,21 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601927</v>
+        <v>601565</v>
       </c>
       <c r="R14" t="n">
-        <v>6926280</v>
+        <v>6926576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982794</v>
+        <v>128982844</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601565</v>
+        <v>601669</v>
       </c>
       <c r="R15" t="n">
-        <v>6926576</v>
+        <v>6926519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2067,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2611,7 +2611,7 @@
         <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982814</v>
+        <v>128982808</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601765</v>
+        <v>601744</v>
       </c>
       <c r="R41" t="n">
-        <v>6926339</v>
+        <v>6926392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982808</v>
+        <v>128982807</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601744</v>
+        <v>601721</v>
       </c>
       <c r="R42" t="n">
-        <v>6926392</v>
+        <v>6926415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128982807</v>
+        <v>128975206</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4900,16 +4900,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601721</v>
+        <v>601689</v>
       </c>
       <c r="R43" t="n">
-        <v>6926415</v>
+        <v>6926299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4946,7 +4951,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4973,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128975206</v>
+        <v>128982831</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5002,21 +5007,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601689</v>
+        <v>601901</v>
       </c>
       <c r="R44" t="n">
-        <v>6926299</v>
+        <v>6926291</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982831</v>
+        <v>128982805</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601901</v>
+        <v>601686</v>
       </c>
       <c r="R45" t="n">
-        <v>6926291</v>
+        <v>6926478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982805</v>
+        <v>128982804</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601686</v>
+        <v>601703</v>
       </c>
       <c r="R46" t="n">
-        <v>6926478</v>
+        <v>6926487</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982804</v>
+        <v>128982814</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601703</v>
+        <v>601765</v>
       </c>
       <c r="R47" t="n">
-        <v>6926487</v>
+        <v>6926339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6322,7 +6322,7 @@
         <v>128975492</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128982843</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982795</v>
+        <v>128982822</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601586</v>
+        <v>601990</v>
       </c>
       <c r="R5" t="n">
-        <v>6926499</v>
+        <v>6926320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982822</v>
+        <v>128982795</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601990</v>
+        <v>601586</v>
       </c>
       <c r="R6" t="n">
-        <v>6926320</v>
+        <v>6926499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982810</v>
+        <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601716</v>
+        <v>601932</v>
       </c>
       <c r="R8" t="n">
-        <v>6926368</v>
+        <v>6926305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982793</v>
+        <v>128982810</v>
       </c>
       <c r="B10" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601932</v>
+        <v>601716</v>
       </c>
       <c r="R10" t="n">
-        <v>6926305</v>
+        <v>6926368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982834</v>
+        <v>128982844</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601669</v>
       </c>
       <c r="R11" t="n">
-        <v>6926585</v>
+        <v>6926519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982830</v>
+        <v>128982834</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,16 +1691,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1720,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601912</v>
+        <v>601569</v>
       </c>
       <c r="R12" t="n">
-        <v>6926296</v>
+        <v>6926585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128975867</v>
+        <v>128982830</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1816,21 +1811,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601927</v>
+        <v>601912</v>
       </c>
       <c r="R13" t="n">
-        <v>6926280</v>
+        <v>6926296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1894,7 +1884,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982794</v>
+        <v>128975867</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1923,16 +1913,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601565</v>
+        <v>601927</v>
       </c>
       <c r="R14" t="n">
-        <v>6926576</v>
+        <v>6926280</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,32 +1991,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982844</v>
+        <v>128982794</v>
       </c>
       <c r="B15" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601669</v>
+        <v>601565</v>
       </c>
       <c r="R15" t="n">
-        <v>6926519</v>
+        <v>6926576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982812</v>
+        <v>128982816</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601710</v>
+        <v>601763</v>
       </c>
       <c r="R16" t="n">
-        <v>6926335</v>
+        <v>6926420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R17" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128982826</v>
+        <v>128975179</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2326,16 +2326,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602022</v>
+        <v>601685</v>
       </c>
       <c r="R18" t="n">
-        <v>6926303</v>
+        <v>6926309</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,7 +2404,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982809</v>
+        <v>128982826</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2434,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601746</v>
+        <v>602022</v>
       </c>
       <c r="R19" t="n">
-        <v>6926365</v>
+        <v>6926303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,7 +2506,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128975179</v>
+        <v>128982809</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2530,21 +2535,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601685</v>
+        <v>601746</v>
       </c>
       <c r="R20" t="n">
-        <v>6926309</v>
+        <v>6926365</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,7 +2611,7 @@
         <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982806</v>
+        <v>128982796</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601714</v>
+        <v>601578</v>
       </c>
       <c r="R26" t="n">
-        <v>6926425</v>
+        <v>6926496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982796</v>
+        <v>128982827</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601578</v>
+        <v>602016</v>
       </c>
       <c r="R27" t="n">
-        <v>6926496</v>
+        <v>6926284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982818</v>
+        <v>128982806</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601845</v>
+        <v>601714</v>
       </c>
       <c r="R28" t="n">
-        <v>6926319</v>
+        <v>6926425</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982827</v>
+        <v>128982818</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602016</v>
+        <v>601845</v>
       </c>
       <c r="R29" t="n">
-        <v>6926284</v>
+        <v>6926319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3734,50 +3734,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128975094</v>
+        <v>128982838</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601680</v>
+        <v>601914</v>
       </c>
       <c r="R32" t="n">
-        <v>6926301</v>
+        <v>6926288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,7 +3836,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982813</v>
+        <v>128975094</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3870,16 +3865,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601751</v>
+        <v>601680</v>
       </c>
       <c r="R33" t="n">
-        <v>6926340</v>
+        <v>6926301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982838</v>
+        <v>128982813</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601914</v>
+        <v>601751</v>
       </c>
       <c r="R34" t="n">
-        <v>6926288</v>
+        <v>6926340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4147,7 +4147,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R36" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982800</v>
+        <v>128982801</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601632</v>
+        <v>601654</v>
       </c>
       <c r="R37" t="n">
-        <v>6926485</v>
+        <v>6926524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982808</v>
+        <v>128982807</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601744</v>
+        <v>601721</v>
       </c>
       <c r="R41" t="n">
-        <v>6926392</v>
+        <v>6926415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982807</v>
+        <v>128982831</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601721</v>
+        <v>601901</v>
       </c>
       <c r="R42" t="n">
-        <v>6926415</v>
+        <v>6926291</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982831</v>
+        <v>128982814</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601901</v>
+        <v>601765</v>
       </c>
       <c r="R44" t="n">
-        <v>6926291</v>
+        <v>6926339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982805</v>
+        <v>128982808</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601686</v>
+        <v>601744</v>
       </c>
       <c r="R45" t="n">
-        <v>6926478</v>
+        <v>6926392</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982814</v>
+        <v>128982805</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601765</v>
+        <v>601686</v>
       </c>
       <c r="R47" t="n">
-        <v>6926339</v>
+        <v>6926478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5590,7 +5590,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982821</v>
+        <v>128982823</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>601965</v>
+        <v>602006</v>
       </c>
       <c r="R50" t="n">
-        <v>6926332</v>
+        <v>6926333</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R51" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R52" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982823</v>
+        <v>128982821</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602006</v>
+        <v>601965</v>
       </c>
       <c r="R53" t="n">
-        <v>6926333</v>
+        <v>6926332</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128975168</v>
+        <v>128982798</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -6037,21 +6037,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601683</v>
+        <v>601625</v>
       </c>
       <c r="R54" t="n">
-        <v>6926321</v>
+        <v>6926480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6088,7 +6083,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,7 +6110,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128982798</v>
+        <v>128975168</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6144,16 +6139,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601625</v>
+        <v>601683</v>
       </c>
       <c r="R55" t="n">
-        <v>6926480</v>
+        <v>6926321</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6322,7 +6322,7 @@
         <v>128975492</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128982843</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982822</v>
+        <v>128982795</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601990</v>
+        <v>601586</v>
       </c>
       <c r="R5" t="n">
-        <v>6926320</v>
+        <v>6926499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982795</v>
+        <v>128982822</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601586</v>
+        <v>601990</v>
       </c>
       <c r="R6" t="n">
-        <v>6926499</v>
+        <v>6926320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
         <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982824</v>
+        <v>128982810</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602020</v>
+        <v>601716</v>
       </c>
       <c r="R9" t="n">
-        <v>6926329</v>
+        <v>6926368</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R10" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982844</v>
+        <v>128982834</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601669</v>
+        <v>601569</v>
       </c>
       <c r="R11" t="n">
-        <v>6926519</v>
+        <v>6926585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982834</v>
+        <v>128982844</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601569</v>
+        <v>601669</v>
       </c>
       <c r="R12" t="n">
-        <v>6926585</v>
+        <v>6926519</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,7 +2093,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982816</v>
+        <v>128982812</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601763</v>
+        <v>601710</v>
       </c>
       <c r="R16" t="n">
-        <v>6926420</v>
+        <v>6926335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982812</v>
+        <v>128982816</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601710</v>
+        <v>601763</v>
       </c>
       <c r="R17" t="n">
-        <v>6926335</v>
+        <v>6926420</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128975179</v>
+        <v>128982826</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2326,21 +2326,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>601685</v>
+        <v>602022</v>
       </c>
       <c r="R18" t="n">
-        <v>6926309</v>
+        <v>6926303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,7 +2399,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982826</v>
+        <v>128982809</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602022</v>
+        <v>601746</v>
       </c>
       <c r="R19" t="n">
-        <v>6926303</v>
+        <v>6926365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,7 +2501,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128982809</v>
+        <v>128975179</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2535,16 +2530,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601746</v>
+        <v>601685</v>
       </c>
       <c r="R20" t="n">
-        <v>6926365</v>
+        <v>6926309</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2810,7 @@
         <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982796</v>
+        <v>128982806</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601578</v>
+        <v>601714</v>
       </c>
       <c r="R26" t="n">
-        <v>6926496</v>
+        <v>6926425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982827</v>
+        <v>128982796</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602016</v>
+        <v>601578</v>
       </c>
       <c r="R27" t="n">
-        <v>6926284</v>
+        <v>6926496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982806</v>
+        <v>128982818</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601714</v>
+        <v>601845</v>
       </c>
       <c r="R28" t="n">
-        <v>6926425</v>
+        <v>6926319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982818</v>
+        <v>128982827</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601845</v>
+        <v>602016</v>
       </c>
       <c r="R29" t="n">
-        <v>6926319</v>
+        <v>6926284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3734,45 +3734,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128982838</v>
+        <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601914</v>
+        <v>601680</v>
       </c>
       <c r="R32" t="n">
-        <v>6926288</v>
+        <v>6926301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128975094</v>
+        <v>128982813</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3865,21 +3870,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601680</v>
+        <v>601751</v>
       </c>
       <c r="R33" t="n">
-        <v>6926301</v>
+        <v>6926340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3943,32 +3943,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982813</v>
+        <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601751</v>
+        <v>601914</v>
       </c>
       <c r="R34" t="n">
-        <v>6926340</v>
+        <v>6926288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4147,7 +4147,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982800</v>
+        <v>128982801</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601632</v>
+        <v>601654</v>
       </c>
       <c r="R36" t="n">
-        <v>6926485</v>
+        <v>6926524</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R37" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982807</v>
+        <v>128975206</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4696,16 +4696,21 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601721</v>
+        <v>601689</v>
       </c>
       <c r="R41" t="n">
-        <v>6926415</v>
+        <v>6926299</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4742,7 +4747,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4871,7 +4876,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128975206</v>
+        <v>128982805</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4900,21 +4905,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601689</v>
+        <v>601686</v>
       </c>
       <c r="R43" t="n">
-        <v>6926299</v>
+        <v>6926478</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982808</v>
+        <v>128982807</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601744</v>
+        <v>601721</v>
       </c>
       <c r="R45" t="n">
-        <v>6926392</v>
+        <v>6926415</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982805</v>
+        <v>128982833</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601686</v>
+        <v>601691</v>
       </c>
       <c r="R47" t="n">
-        <v>6926478</v>
+        <v>6926349</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128982833</v>
+        <v>128982808</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601691</v>
+        <v>601744</v>
       </c>
       <c r="R48" t="n">
-        <v>6926349</v>
+        <v>6926392</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5590,7 +5590,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982823</v>
+        <v>128982821</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602006</v>
+        <v>601965</v>
       </c>
       <c r="R50" t="n">
-        <v>6926333</v>
+        <v>6926332</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975260</v>
+        <v>128975363</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601702</v>
+        <v>601787</v>
       </c>
       <c r="R51" t="n">
-        <v>6926319</v>
+        <v>6926265</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975363</v>
+        <v>128975260</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601787</v>
+        <v>601702</v>
       </c>
       <c r="R52" t="n">
-        <v>6926265</v>
+        <v>6926319</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982821</v>
+        <v>128982823</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>601965</v>
+        <v>602006</v>
       </c>
       <c r="R53" t="n">
-        <v>6926332</v>
+        <v>6926333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128982798</v>
+        <v>128975168</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -6037,16 +6037,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601625</v>
+        <v>601683</v>
       </c>
       <c r="R54" t="n">
-        <v>6926480</v>
+        <v>6926321</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6083,7 +6088,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6110,7 +6115,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128975168</v>
+        <v>128982798</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6139,21 +6144,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601683</v>
+        <v>601625</v>
       </c>
       <c r="R55" t="n">
-        <v>6926321</v>
+        <v>6926480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128982836</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128982793</v>
       </c>
       <c r="B8" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982844</v>
+        <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601669</v>
+        <v>601912</v>
       </c>
       <c r="R12" t="n">
-        <v>6926519</v>
+        <v>6926296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128982830</v>
+        <v>128975867</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1811,16 +1816,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601912</v>
+        <v>601927</v>
       </c>
       <c r="R13" t="n">
-        <v>6926296</v>
+        <v>6926280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1867,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,7 +1894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128975867</v>
+        <v>128982794</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1913,21 +1923,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601927</v>
+        <v>601565</v>
       </c>
       <c r="R14" t="n">
-        <v>6926280</v>
+        <v>6926576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982794</v>
+        <v>128982844</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601565</v>
+        <v>601669</v>
       </c>
       <c r="R15" t="n">
-        <v>6926576</v>
+        <v>6926519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,11 +2067,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,45 +2608,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982840</v>
+        <v>128975896</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601810</v>
+        <v>601925</v>
       </c>
       <c r="R21" t="n">
-        <v>6926372</v>
+        <v>6926296</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,49 +2811,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128975896</v>
+        <v>128982840</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601925</v>
+        <v>601810</v>
       </c>
       <c r="R23" t="n">
-        <v>6926296</v>
+        <v>6926372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982818</v>
+        <v>128982827</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601845</v>
+        <v>602016</v>
       </c>
       <c r="R28" t="n">
-        <v>6926319</v>
+        <v>6926284</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982827</v>
+        <v>128982818</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602016</v>
+        <v>601845</v>
       </c>
       <c r="R29" t="n">
-        <v>6926284</v>
+        <v>6926319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3946,7 +3946,7 @@
         <v>128982838</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128982802</v>
+        <v>128982801</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601670</v>
+        <v>601654</v>
       </c>
       <c r="R35" t="n">
-        <v>6926508</v>
+        <v>6926524</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982801</v>
+        <v>128982800</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601654</v>
+        <v>601632</v>
       </c>
       <c r="R36" t="n">
-        <v>6926524</v>
+        <v>6926485</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982800</v>
+        <v>128982802</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601632</v>
+        <v>601670</v>
       </c>
       <c r="R37" t="n">
-        <v>6926485</v>
+        <v>6926508</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128975206</v>
+        <v>128982808</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4696,21 +4696,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601689</v>
+        <v>601744</v>
       </c>
       <c r="R41" t="n">
-        <v>6926299</v>
+        <v>6926392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4747,7 +4742,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4774,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982831</v>
+        <v>128982807</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4809,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601901</v>
+        <v>601721</v>
       </c>
       <c r="R42" t="n">
-        <v>6926291</v>
+        <v>6926415</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,7 +4844,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4876,7 +4871,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128982805</v>
+        <v>128975206</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4905,16 +4900,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601686</v>
+        <v>601689</v>
       </c>
       <c r="R43" t="n">
-        <v>6926478</v>
+        <v>6926299</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982814</v>
+        <v>128982831</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601765</v>
+        <v>601901</v>
       </c>
       <c r="R44" t="n">
-        <v>6926339</v>
+        <v>6926291</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982807</v>
+        <v>128982805</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601721</v>
+        <v>601686</v>
       </c>
       <c r="R45" t="n">
-        <v>6926415</v>
+        <v>6926478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982833</v>
+        <v>128982814</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601691</v>
+        <v>601765</v>
       </c>
       <c r="R47" t="n">
-        <v>6926349</v>
+        <v>6926339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128982808</v>
+        <v>128982833</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601744</v>
+        <v>601691</v>
       </c>
       <c r="R48" t="n">
-        <v>6926392</v>
+        <v>6926349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982834</v>
+        <v>128982844</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601569</v>
+        <v>601669</v>
       </c>
       <c r="R11" t="n">
-        <v>6926585</v>
+        <v>6926519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1996,32 +1991,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982844</v>
+        <v>128982834</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601669</v>
+        <v>601569</v>
       </c>
       <c r="R15" t="n">
-        <v>6926519</v>
+        <v>6926585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,6 +2062,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,49 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128975896</v>
+        <v>128982840</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601925</v>
+        <v>601810</v>
       </c>
       <c r="R21" t="n">
-        <v>6926296</v>
+        <v>6926372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,45 +2807,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128982840</v>
+        <v>128975896</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601810</v>
+        <v>601925</v>
       </c>
       <c r="R23" t="n">
-        <v>6926372</v>
+        <v>6926296</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982806</v>
+        <v>128982827</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601714</v>
+        <v>602016</v>
       </c>
       <c r="R26" t="n">
-        <v>6926425</v>
+        <v>6926284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982796</v>
+        <v>128982806</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601578</v>
+        <v>601714</v>
       </c>
       <c r="R27" t="n">
-        <v>6926496</v>
+        <v>6926425</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982827</v>
+        <v>128982796</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602016</v>
+        <v>601578</v>
       </c>
       <c r="R28" t="n">
-        <v>6926284</v>
+        <v>6926496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128982832</v>
+        <v>128975410</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3554,16 +3554,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601911</v>
+        <v>601764</v>
       </c>
       <c r="R30" t="n">
-        <v>6926297</v>
+        <v>6926247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,7 +3605,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3627,7 +3632,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128975410</v>
+        <v>128982832</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3656,21 +3661,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601764</v>
+        <v>601911</v>
       </c>
       <c r="R31" t="n">
-        <v>6926247</v>
+        <v>6926297</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4458,7 +4458,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128982820</v>
+        <v>128975430</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4487,16 +4487,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601839</v>
+        <v>601742</v>
       </c>
       <c r="R39" t="n">
-        <v>6926335</v>
+        <v>6926230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4533,7 +4538,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4560,7 +4565,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128975430</v>
+        <v>128982820</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4589,21 +4594,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601742</v>
+        <v>601839</v>
       </c>
       <c r="R40" t="n">
-        <v>6926230</v>
+        <v>6926335</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4769,7 +4769,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128982807</v>
+        <v>128975206</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4798,16 +4798,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601721</v>
+        <v>601689</v>
       </c>
       <c r="R42" t="n">
-        <v>6926415</v>
+        <v>6926299</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,7 +4849,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4871,7 +4876,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128975206</v>
+        <v>128982833</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4900,21 +4905,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601689</v>
+        <v>601691</v>
       </c>
       <c r="R43" t="n">
-        <v>6926299</v>
+        <v>6926349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4978,7 +4978,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982831</v>
+        <v>128982807</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601901</v>
+        <v>601721</v>
       </c>
       <c r="R44" t="n">
-        <v>6926291</v>
+        <v>6926415</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982805</v>
+        <v>128982831</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601686</v>
+        <v>601901</v>
       </c>
       <c r="R45" t="n">
-        <v>6926478</v>
+        <v>6926291</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982804</v>
+        <v>128982805</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601703</v>
+        <v>601686</v>
       </c>
       <c r="R46" t="n">
-        <v>6926487</v>
+        <v>6926478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982814</v>
+        <v>128982804</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601765</v>
+        <v>601703</v>
       </c>
       <c r="R47" t="n">
-        <v>6926339</v>
+        <v>6926487</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128982833</v>
+        <v>128982814</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601691</v>
+        <v>601765</v>
       </c>
       <c r="R48" t="n">
-        <v>6926349</v>
+        <v>6926339</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982793</v>
+        <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601932</v>
+        <v>601716</v>
       </c>
       <c r="R8" t="n">
-        <v>6926305</v>
+        <v>6926368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1353,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982810</v>
+        <v>128982824</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1414,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601716</v>
+        <v>602020</v>
       </c>
       <c r="R9" t="n">
-        <v>6926368</v>
+        <v>6926329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982824</v>
+        <v>128982793</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602020</v>
+        <v>601932</v>
       </c>
       <c r="R10" t="n">
-        <v>6926329</v>
+        <v>6926305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1557,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982827</v>
+        <v>128982806</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602016</v>
+        <v>601714</v>
       </c>
       <c r="R26" t="n">
-        <v>6926284</v>
+        <v>6926425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982806</v>
+        <v>128982796</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601714</v>
+        <v>601578</v>
       </c>
       <c r="R27" t="n">
-        <v>6926425</v>
+        <v>6926496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982796</v>
+        <v>128982818</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601578</v>
+        <v>601845</v>
       </c>
       <c r="R28" t="n">
-        <v>6926496</v>
+        <v>6926319</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982818</v>
+        <v>128982827</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>601845</v>
+        <v>602016</v>
       </c>
       <c r="R29" t="n">
-        <v>6926319</v>
+        <v>6926284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128975410</v>
+        <v>128982832</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3554,21 +3554,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601764</v>
+        <v>601911</v>
       </c>
       <c r="R30" t="n">
-        <v>6926247</v>
+        <v>6926297</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,7 +3600,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,7 +3627,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128982832</v>
+        <v>128975410</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3661,16 +3656,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601911</v>
+        <v>601764</v>
       </c>
       <c r="R31" t="n">
-        <v>6926297</v>
+        <v>6926247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128982817</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128982825</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128982795</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128982822</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128982811</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128982824</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>128975867</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128982794</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>128982812</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128982816</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>128982826</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128982809</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>128975179</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128982828</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>128975731</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128982819</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128982806</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128982796</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128982818</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128982827</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>128982832</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>128975410</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128982813</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>128982801</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>128982800</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128982802</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>128975670</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>128975430</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>128982820</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>128982808</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>128975206</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>128982833</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>128982807</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>128982831</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128982805</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>128982804</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>128982814</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128982797</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>128982821</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128975363</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128975260</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>128982823</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>128975168</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>128982798</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>128982815</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128982817</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128982825</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128982795</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>128982822</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128982811</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128982810</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128982824</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>128982830</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>128975867</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>128982794</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>128982812</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128982816</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>128982826</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128982809</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>128975179</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128982828</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>128975731</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128982819</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128982806</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>128982796</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128982818</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>128982827</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>128982832</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>128975410</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>128975094</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>128982813</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>128982801</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>128982800</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>128982802</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>128975670</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>128975430</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>128982820</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>128982808</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>128975206</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>128982833</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>128982807</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>128982831</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>128982805</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>128982804</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>128982814</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>128982797</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>128982821</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>128975363</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128975260</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>128982823</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>128975168</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>128982798</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>128982815</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128982836</v>
+        <v>128982793</v>
       </c>
       <c r="B2" t="n">
-        <v>97595</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601939</v>
+        <v>601932</v>
       </c>
       <c r="R2" t="n">
-        <v>6926358</v>
+        <v>6926305</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128982817</v>
+        <v>128975492</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601807</v>
+        <v>601788</v>
       </c>
       <c r="R3" t="n">
-        <v>6926447</v>
+        <v>6926222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128982825</v>
+        <v>128982840</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602015</v>
+        <v>601810</v>
       </c>
       <c r="R4" t="n">
-        <v>6926321</v>
+        <v>6926372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128982795</v>
+        <v>128982843</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601586</v>
+        <v>602016</v>
       </c>
       <c r="R5" t="n">
-        <v>6926499</v>
+        <v>6926328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128982822</v>
+        <v>128982844</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601990</v>
+        <v>601669</v>
       </c>
       <c r="R6" t="n">
-        <v>6926320</v>
+        <v>6926519</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,27 +1160,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128982811</v>
+        <v>128982834</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1215,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601708</v>
+        <v>601569</v>
       </c>
       <c r="R7" t="n">
-        <v>6926340</v>
+        <v>6926585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1235,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128982810</v>
+        <v>128975008</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,16 +1291,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601716</v>
+        <v>601650</v>
       </c>
       <c r="R8" t="n">
-        <v>6926368</v>
+        <v>6926287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1342,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128982824</v>
+        <v>128975035</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,16 +1398,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602020</v>
+        <v>601656</v>
       </c>
       <c r="R9" t="n">
-        <v>6926329</v>
+        <v>6926299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,45 +1476,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128982793</v>
+        <v>128975094</v>
       </c>
       <c r="B10" t="n">
-        <v>91514</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601932</v>
+        <v>601680</v>
       </c>
       <c r="R10" t="n">
-        <v>6926305</v>
+        <v>6926301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,45 +1583,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128982844</v>
+        <v>128975124</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601669</v>
+        <v>601685</v>
       </c>
       <c r="R11" t="n">
-        <v>6926519</v>
+        <v>6926309</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1659,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128982830</v>
+        <v>128975168</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,16 +1719,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601912</v>
+        <v>601683</v>
       </c>
       <c r="R12" t="n">
-        <v>6926296</v>
+        <v>6926321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128975867</v>
+        <v>128975206</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,7 +1828,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1822,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601927</v>
+        <v>601689</v>
       </c>
       <c r="R13" t="n">
-        <v>6926280</v>
+        <v>6926299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128982794</v>
+        <v>128975260</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,16 +1933,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601565</v>
+        <v>601702</v>
       </c>
       <c r="R14" t="n">
-        <v>6926576</v>
+        <v>6926319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1984,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128982834</v>
+        <v>128975363</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,16 +2022,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2020,16 +2040,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601569</v>
+        <v>601787</v>
       </c>
       <c r="R15" t="n">
-        <v>6926585</v>
+        <v>6926265</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2091,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Förbiflygande</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128982812</v>
+        <v>128975410</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2122,16 +2147,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>601710</v>
+        <v>601764</v>
       </c>
       <c r="R16" t="n">
-        <v>6926335</v>
+        <v>6926247</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128982816</v>
+        <v>128975430</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,16 +2254,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>601763</v>
+        <v>601742</v>
       </c>
       <c r="R17" t="n">
-        <v>6926420</v>
+        <v>6926230</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2305,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128982826</v>
+        <v>128975670</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2326,16 +2361,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602022</v>
+        <v>601875</v>
       </c>
       <c r="R18" t="n">
-        <v>6926303</v>
+        <v>6926213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2412,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128982809</v>
+        <v>128975731</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,16 +2468,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckegrensbodarna, Mpd</t>
+          <t>Skarpåsen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>601746</v>
+        <v>601908</v>
       </c>
       <c r="R19" t="n">
-        <v>6926365</v>
+        <v>6926265</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2519,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128975179</v>
+        <v>128975811</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,7 +2577,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2541,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>601685</v>
+        <v>601927</v>
       </c>
       <c r="R20" t="n">
-        <v>6926309</v>
+        <v>6926280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128982840</v>
+        <v>128982794</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2643,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>601810</v>
+        <v>601565</v>
       </c>
       <c r="R21" t="n">
-        <v>6926372</v>
+        <v>6926576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2724,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128982828</v>
+        <v>128982795</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>601953</v>
+        <v>601586</v>
       </c>
       <c r="R22" t="n">
-        <v>6926305</v>
+        <v>6926499</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,49 +2857,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128975896</v>
+        <v>128982796</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>601925</v>
+        <v>601578</v>
       </c>
       <c r="R23" t="n">
-        <v>6926296</v>
+        <v>6926496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,6 +2928,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2908,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128975731</v>
+        <v>128982797</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2988,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>601908</v>
+        <v>601592</v>
       </c>
       <c r="R24" t="n">
-        <v>6926265</v>
+        <v>6926483</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2988,7 +3034,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3015,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128982819</v>
+        <v>128982798</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>601851</v>
+        <v>601625</v>
       </c>
       <c r="R25" t="n">
-        <v>6926322</v>
+        <v>6926480</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128982806</v>
+        <v>128982799</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3152,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>601714</v>
+        <v>601632</v>
       </c>
       <c r="R26" t="n">
-        <v>6926425</v>
+        <v>6926477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128982796</v>
+        <v>128982800</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>601578</v>
+        <v>601632</v>
       </c>
       <c r="R27" t="n">
-        <v>6926496</v>
+        <v>6926485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,7 +3340,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3321,10 +3367,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128982818</v>
+        <v>128982801</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>601845</v>
+        <v>601654</v>
       </c>
       <c r="R28" t="n">
-        <v>6926319</v>
+        <v>6926524</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128982827</v>
+        <v>128982802</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602016</v>
+        <v>601670</v>
       </c>
       <c r="R29" t="n">
-        <v>6926284</v>
+        <v>6926508</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3525,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128982832</v>
+        <v>128982804</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3560,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>601911</v>
+        <v>601703</v>
       </c>
       <c r="R30" t="n">
-        <v>6926297</v>
+        <v>6926487</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3627,10 +3673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128975410</v>
+        <v>128982805</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3656,21 +3702,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>601764</v>
+        <v>601686</v>
       </c>
       <c r="R31" t="n">
-        <v>6926247</v>
+        <v>6926478</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,7 +3748,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3734,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128975094</v>
+        <v>128982806</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3763,21 +3804,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>601680</v>
+        <v>601714</v>
       </c>
       <c r="R32" t="n">
-        <v>6926301</v>
+        <v>6926425</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,7 +3850,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3841,10 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128982813</v>
+        <v>128982807</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3876,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>601751</v>
+        <v>601721</v>
       </c>
       <c r="R33" t="n">
-        <v>6926340</v>
+        <v>6926415</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3943,32 +3979,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128982838</v>
+        <v>128982808</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +4014,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>601914</v>
+        <v>601744</v>
       </c>
       <c r="R34" t="n">
-        <v>6926288</v>
+        <v>6926392</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,7 +4054,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4045,10 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128982801</v>
+        <v>128982809</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4080,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>601654</v>
+        <v>601746</v>
       </c>
       <c r="R35" t="n">
-        <v>6926524</v>
+        <v>6926365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4147,10 +4183,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128982800</v>
+        <v>128982810</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4182,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>601632</v>
+        <v>601716</v>
       </c>
       <c r="R36" t="n">
-        <v>6926485</v>
+        <v>6926368</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,7 +4258,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128982802</v>
+        <v>128982811</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4284,10 +4320,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>601670</v>
+        <v>601708</v>
       </c>
       <c r="R37" t="n">
-        <v>6926508</v>
+        <v>6926340</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4324,7 +4360,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4351,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128975670</v>
+        <v>128982812</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4380,21 +4416,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>601875</v>
+        <v>601710</v>
       </c>
       <c r="R38" t="n">
-        <v>6926213</v>
+        <v>6926335</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4431,7 +4462,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4458,10 +4489,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128975430</v>
+        <v>128982813</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,21 +4518,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>601742</v>
+        <v>601751</v>
       </c>
       <c r="R39" t="n">
-        <v>6926230</v>
+        <v>6926340</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4538,7 +4564,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4565,10 +4591,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128982820</v>
+        <v>128982814</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4600,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>601839</v>
+        <v>601765</v>
       </c>
       <c r="R40" t="n">
-        <v>6926335</v>
+        <v>6926339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4640,7 +4666,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4667,10 +4693,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128982808</v>
+        <v>128982815</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4702,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>601744</v>
+        <v>601761</v>
       </c>
       <c r="R41" t="n">
-        <v>6926392</v>
+        <v>6926386</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128975206</v>
+        <v>128982816</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4798,21 +4824,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>601689</v>
+        <v>601763</v>
       </c>
       <c r="R42" t="n">
-        <v>6926299</v>
+        <v>6926420</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,7 +4870,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4876,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128982833</v>
+        <v>128982817</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4911,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>601691</v>
+        <v>601807</v>
       </c>
       <c r="R43" t="n">
-        <v>6926349</v>
+        <v>6926447</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128982807</v>
+        <v>128982818</v>
       </c>
       <c r="B44" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5013,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>601721</v>
+        <v>601845</v>
       </c>
       <c r="R44" t="n">
-        <v>6926415</v>
+        <v>6926319</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128982831</v>
+        <v>128982819</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5115,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>601901</v>
+        <v>601851</v>
       </c>
       <c r="R45" t="n">
-        <v>6926291</v>
+        <v>6926322</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,7 +5176,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5182,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128982805</v>
+        <v>128982820</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5217,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>601686</v>
+        <v>601839</v>
       </c>
       <c r="R46" t="n">
-        <v>6926478</v>
+        <v>6926335</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5257,7 +5278,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5284,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128982804</v>
+        <v>128982821</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5319,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>601703</v>
+        <v>601965</v>
       </c>
       <c r="R47" t="n">
-        <v>6926487</v>
+        <v>6926332</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128982814</v>
+        <v>128982822</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5421,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>601765</v>
+        <v>601990</v>
       </c>
       <c r="R48" t="n">
-        <v>6926339</v>
+        <v>6926320</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5461,7 +5482,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5488,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128982797</v>
+        <v>128982823</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5523,10 +5544,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>601592</v>
+        <v>602006</v>
       </c>
       <c r="R49" t="n">
-        <v>6926483</v>
+        <v>6926333</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5563,7 +5584,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5590,10 +5611,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128982821</v>
+        <v>128982824</v>
       </c>
       <c r="B50" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5625,10 +5646,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>601965</v>
+        <v>602020</v>
       </c>
       <c r="R50" t="n">
-        <v>6926332</v>
+        <v>6926329</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5686,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5692,10 +5713,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128975363</v>
+        <v>128982825</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5721,21 +5742,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>601787</v>
+        <v>602015</v>
       </c>
       <c r="R51" t="n">
-        <v>6926265</v>
+        <v>6926321</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5788,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,10 +5815,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128975260</v>
+        <v>128982826</v>
       </c>
       <c r="B52" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5828,21 +5844,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>601702</v>
+        <v>602022</v>
       </c>
       <c r="R52" t="n">
-        <v>6926319</v>
+        <v>6926303</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5879,7 +5890,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5906,10 +5917,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128982823</v>
+        <v>128982827</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5941,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602006</v>
+        <v>602016</v>
       </c>
       <c r="R53" t="n">
-        <v>6926333</v>
+        <v>6926284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,10 +6019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128975168</v>
+        <v>128982828</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6037,21 +6048,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>601683</v>
+        <v>601953</v>
       </c>
       <c r="R54" t="n">
-        <v>6926321</v>
+        <v>6926305</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6088,7 +6094,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6115,10 +6121,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128982798</v>
+        <v>128982830</v>
       </c>
       <c r="B55" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6150,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>601625</v>
+        <v>601912</v>
       </c>
       <c r="R55" t="n">
-        <v>6926480</v>
+        <v>6926296</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6190,7 +6196,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6217,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128982815</v>
+        <v>128982831</v>
       </c>
       <c r="B56" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,10 +6258,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>601761</v>
+        <v>601901</v>
       </c>
       <c r="R56" t="n">
-        <v>6926386</v>
+        <v>6926291</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6292,7 +6298,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6319,10 +6325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128975492</v>
+        <v>128982832</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6330,34 +6336,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skarpåsen, Mpd</t>
+          <t>Bäckegrensbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>601788</v>
+        <v>601911</v>
       </c>
       <c r="R57" t="n">
-        <v>6926222</v>
+        <v>6926297</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6390,6 +6396,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6416,10 +6427,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128982843</v>
+        <v>128982833</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6427,21 +6438,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6451,10 +6462,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602016</v>
+        <v>601691</v>
       </c>
       <c r="R58" t="n">
-        <v>6926328</v>
+        <v>6926349</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,6 +6500,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6510,6 +6526,306 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128975896</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skarpåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>601925</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6926296</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128982838</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bäckegrensbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>601914</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6926288</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>45 ex</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128982836</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bäckegrensbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>601939</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6926358</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38443-2025 artfynd.xlsx
+++ b/artfynd/A 38443-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982793</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975035</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975124</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975168</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975206</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975260</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975363</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975410</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2436,6 +2521,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975670</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975731</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2650,6 +2745,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975811</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2752,6 +2852,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982794</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2854,6 +2959,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982795</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2956,6 +3066,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982796</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3058,6 +3173,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982797</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3160,6 +3280,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982798</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982799</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3364,6 +3494,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982800</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3466,6 +3601,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982801</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3568,6 +3708,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982802</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3670,6 +3815,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982804</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3772,6 +3922,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982805</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3874,6 +4029,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982806</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3976,6 +4136,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982807</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4078,6 +4243,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982808</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4180,6 +4350,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982809</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4282,6 +4457,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982810</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4384,6 +4564,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982811</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4486,6 +4671,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982812</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4588,6 +4778,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982813</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4690,6 +4885,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982814</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4792,6 +4992,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982815</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4894,6 +5099,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982816</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4996,6 +5206,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982817</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5098,6 +5313,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982818</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5200,6 +5420,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982819</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5302,6 +5527,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982820</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5404,6 +5634,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982821</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5506,6 +5741,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982822</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5608,6 +5848,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982823</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5710,6 +5955,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982824</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5812,6 +6062,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982825</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5914,6 +6169,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982826</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6016,6 +6276,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982827</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6118,6 +6383,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982828</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6220,6 +6490,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982830</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6322,6 +6597,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982831</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6424,6 +6704,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982832</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6526,6 +6811,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982833</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6627,6 +6917,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128975896</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6729,6 +7024,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982838</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6826,8 +7126,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128982836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>